--- a/data/foodwebData.xlsx
+++ b/data/foodwebData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\michelet\Documents\GitHub\trophicNetworkFN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9ED815-146D-4DB4-B620-D9498070B992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5C2B50-374F-438E-9D09-A9CB9A6F0AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4EF2D350-9CF9-4D35-86E2-1B999D3D33F3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{4EF2D350-9CF9-4D35-86E2-1B999D3D33F3}"/>
   </bookViews>
   <sheets>
     <sheet name="mapping" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="309">
   <si>
     <t>Mammals</t>
   </si>
@@ -1916,7 +1916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B34D4177-0819-49FF-A114-9AD432CF4522}">
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr defaultColWidth="40.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1935,13 +1935,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>58</v>
+        <v>271</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -1949,13 +1949,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -1963,27 +1963,27 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>0</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -2005,13 +2005,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>56</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>207</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>55</v>
@@ -2047,13 +2047,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>56</v>
@@ -2075,13 +2075,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>236</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -2089,13 +2089,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -2103,13 +2103,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>37</v>
+        <v>236</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
@@ -2117,13 +2117,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>274</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
@@ -2131,13 +2131,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
@@ -2145,24 +2145,24 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>201</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>237</v>
+        <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
-        <v>233</v>
+      <c r="A18" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>56</v>
@@ -2173,13 +2173,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>203</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
@@ -2187,27 +2187,27 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>61</v>
+      <c r="A21" s="18" t="s">
+        <v>277</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
@@ -2215,24 +2215,24 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>31</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>31</v>
+      <c r="A23" s="18" t="s">
+        <v>233</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>56</v>
@@ -2243,13 +2243,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
@@ -2257,13 +2257,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
@@ -2271,24 +2271,24 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>95</v>
+      <c r="A27" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>56</v>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>209</v>
+        <v>31</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>56</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>56</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>56</v>
@@ -2341,24 +2341,24 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>44</v>
+      <c r="A32" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>56</v>
@@ -2368,28 +2368,28 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>98</v>
+      <c r="A33" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="D33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D34" t="b">
         <v>1</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>56</v>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>210</v>
+        <v>41</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>56</v>
@@ -2425,41 +2425,41 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="D37" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>80</v>
+      <c r="A38" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>98</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="D39" t="b">
         <v>1</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>56</v>
@@ -2481,13 +2481,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>69</v>
+        <v>210</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D41" t="b">
         <v>1</v>
@@ -2495,27 +2495,27 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>206</v>
+        <v>80</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="D42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D43" t="b">
         <v>1</v>
@@ -2523,13 +2523,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>39</v>
+        <v>278</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D44" t="b">
         <v>1</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>56</v>
@@ -2551,38 +2551,38 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D46" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="16" t="s">
-        <v>208</v>
+      <c r="A47" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>56</v>
+        <v>206</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="D47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>208</v>
+        <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>56</v>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D49" t="b">
         <v>1</v>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>56</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>56</v>
@@ -2634,14 +2634,14 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>71</v>
+      <c r="A52" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>68</v>
+        <v>235</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D52" t="b">
         <v>1</v>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D53" t="b">
         <v>1</v>
@@ -2663,13 +2663,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="D54" t="b">
         <v>1</v>
@@ -2677,10 +2677,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>56</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>56</v>
@@ -2705,13 +2705,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D57" t="b">
         <v>1</v>
@@ -2719,13 +2719,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D58" t="b">
         <v>1</v>
@@ -2733,13 +2733,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>195</v>
+        <v>13</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D59" t="b">
         <v>1</v>
@@ -2747,13 +2747,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D60" t="b">
         <v>1</v>
@@ -2761,13 +2761,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="D61" t="b">
         <v>1</v>
@@ -2775,13 +2775,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D62" t="b">
         <v>1</v>
@@ -2789,13 +2789,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>64</v>
+        <v>212</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D63" t="b">
         <v>1</v>
@@ -2803,13 +2803,13 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D64" t="b">
         <v>1</v>
@@ -2817,13 +2817,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D65" t="b">
         <v>1</v>
@@ -2831,13 +2831,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>49</v>
+        <v>275</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D66" t="b">
         <v>1</v>
@@ -2845,27 +2845,27 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="D67" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B68" s="16" t="s">
-        <v>96</v>
+      <c r="A68" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D68" t="b">
         <v>1</v>
@@ -2873,13 +2873,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>197</v>
+        <v>64</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="D69" t="b">
         <v>1</v>
@@ -2887,13 +2887,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="D70" t="b">
         <v>1</v>
@@ -2901,13 +2901,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>7</v>
+        <v>202</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>90</v>
+        <v>238</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="D71" t="b">
         <v>1</v>
@@ -2915,41 +2915,41 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="D72" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>232</v>
+      <c r="A73" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" s="16" t="s">
-        <v>15</v>
+        <v>75</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="D73" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" s="16" t="s">
-        <v>15</v>
+      <c r="A74" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="D74" t="b">
         <v>1</v>
@@ -2957,13 +2957,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>6</v>
+        <v>197</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D75" t="b">
         <v>1</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>196</v>
+        <v>10</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>90</v>
@@ -2984,14 +2984,14 @@
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>82</v>
+      <c r="A77" s="18" t="s">
+        <v>257</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D77" t="b">
         <v>1</v>
@@ -2999,40 +2999,40 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D78" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="16" t="s">
-        <v>204</v>
+      <c r="A79" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D79" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>16</v>
+      <c r="A80" s="16" t="s">
+        <v>232</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C80" s="18" t="s">
         <v>15</v>
       </c>
       <c r="D80" t="b">
@@ -3040,25 +3040,25 @@
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B81" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>56</v>
+      <c r="A81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>15</v>
       </c>
       <c r="D81" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="16" t="s">
-        <v>231</v>
+      <c r="A82" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>0</v>
@@ -3068,14 +3068,14 @@
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="16" t="s">
-        <v>234</v>
+      <c r="A83" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D83" t="b">
         <v>1</v>
@@ -3083,13 +3083,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D84" t="b">
         <v>1</v>
@@ -3097,13 +3097,13 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>199</v>
+        <v>279</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="D85" t="b">
         <v>1</v>
@@ -3111,27 +3111,27 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>17</v>
+        <v>204</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="D86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>4</v>
+        <v>270</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="D87" t="b">
         <v>1</v>
@@ -3139,97 +3139,97 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="C88" s="18" t="s">
+        <v>15</v>
       </c>
       <c r="D88" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>23</v>
+      <c r="A89" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>97</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="D89" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>26</v>
+      <c r="A90" s="18" t="s">
+        <v>231</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D90" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>28</v>
+      <c r="A91" s="18" t="s">
+        <v>234</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D91" t="b">
+        <v>76</v>
+      </c>
+      <c r="D91" s="16" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D92" t="b">
+        <v>56</v>
+      </c>
+      <c r="D92" s="16" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>83</v>
+        <v>199</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D93" t="b">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="D93" s="16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="D94" s="16" t="b">
         <v>1</v>
@@ -3237,13 +3237,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="D95" s="16" t="b">
         <v>1</v>
@@ -3251,69 +3251,69 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D96" s="16" t="b">
+        <v>21</v>
+      </c>
+      <c r="D96" s="18" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D97" s="16" t="b">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="D97" s="18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D98" s="16" t="b">
+      <c r="D98" s="18" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>257</v>
+      <c r="A99" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="D99" s="18" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>267</v>
+      <c r="A100" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D100" s="18" t="b">
         <v>1</v>
@@ -3321,24 +3321,24 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>270</v>
+        <v>83</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D101" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>76</v>
@@ -3349,10 +3349,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>274</v>
+        <v>78</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>76</v>
@@ -3363,13 +3363,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>275</v>
+        <v>5</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D104" s="18" t="b">
         <v>1</v>
@@ -3377,92 +3377,49 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>277</v>
+        <v>85</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D105" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D106" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>279</v>
+        <v>53</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="D107" s="18" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>85</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D108" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D109" s="18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D110" s="18" t="b">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D98">
-    <sortCondition ref="A2:A98"/>
-    <sortCondition ref="B2:B98"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D107">
+    <sortCondition ref="A1:A107"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
